--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,4136 +436,3520 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
+          <t>DR-157</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1708074534161491</v>
+        <v>0.7186495176848875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1867283950617284</v>
+        <v>0.745928338762215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2437888198757764</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5500770416024653</v>
+        <v>0.9983388704318937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7452229299363057</v>
+        <v>0.7819672131147541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5484351713859911</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5371517027863777</v>
+        <v>0.006493506493506494</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5296875</v>
+        <v>0.1745513866231648</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8515625</v>
+        <v>0.7287581699346405</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8091603053435115</v>
+        <v>0.7907348242811502</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.7245222929936306</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08722741433021806</v>
+        <v>0.09951060358890701</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1829457364341085</v>
+        <v>0.7207062600321027</v>
       </c>
       <c r="P2" t="n">
-        <v>0.634375</v>
+        <v>0.2163461538461539</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5579598145285936</v>
+        <v>0.01615508885298869</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9829192546583851</v>
+        <v>0.1231527093596059</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2376395534290271</v>
+        <v>0.1636952998379254</v>
       </c>
       <c r="T2" t="n">
-        <v>0.575</v>
+        <v>0.7430340557275542</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0.2159264931087289</v>
       </c>
       <c r="V2" t="n">
-        <v>0.82642089093702</v>
+        <v>0.7633228840125392</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1715610510046368</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1796875</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1472868217054264</v>
+        <v>0.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.171474358974359</v>
+        <v>0.2067226890756302</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1984126984126984</v>
+        <v>0.2192429022082019</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.499194847020934</v>
+        <v>0.209375</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1656346749226006</v>
+        <v>0.2279293739967897</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1664074650077761</v>
+        <v>0.231139646869984</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2229102167182662</v>
+        <v>0.239344262295082</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.8212121212121212</v>
+        <v>0.2071778140293638</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1648522550544324</v>
+        <v>0.008090614886731391</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1690140845070423</v>
+        <v>0.7675941080196399</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1708860759493671</v>
+        <v>0.2098569157392687</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1700468018720749</v>
+        <v>0.006482982171799027</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1623277182235835</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.1748878923766816</v>
+        <v>0.2249190938511327</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.174922600619195</v>
+        <v>0.2070707070707071</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1706948640483384</v>
+        <v>0.2191558441558442</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1622464898595944</v>
+        <v>0.9379084967320261</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1591591591591592</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.1794478527607362</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.15600624024961</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.170015455950541</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.1773940345368917</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.1689497716894977</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.2372611464968153</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.1677215189873418</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.7420333839150227</v>
+        <v>0.2106109324758842</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1708074534161491</v>
+        <v>0.7186495176848875</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9844961240310077</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9523052464228935</v>
+        <v>0.724709784411277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.7680921052631579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01271860095389507</v>
+        <v>0.998330550918197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01975683890577508</v>
+        <v>0.001620745542949757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009302325581395349</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03645007923930269</v>
+        <v>0.2669902912621359</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0420032310177706</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02311248073959938</v>
+        <v>0.9984</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04458598726114649</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6253968253968254</v>
+        <v>0.1996699669966997</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9796875</v>
+        <v>0.9983844911147012</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0064</v>
+        <v>0.2987220447284345</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2110236220472441</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.3674496644295302</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9546191247974068</v>
+        <v>0.4121510673234811</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02369668246445497</v>
+        <v>0.9984152139461173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3006230529595015</v>
+        <v>0.2904689863842663</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04037267080745342</v>
+        <v>0.9936406995230525</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9904458598726115</v>
+        <v>0.4446254071661238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9937205651491365</v>
+        <v>0.2898550724637681</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9904912836767037</v>
+        <v>0.2840531561461794</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9904306220095693</v>
+        <v>0.2974789915966387</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.971107544141252</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.3131955484896661</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9906542056074766</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9875195007800313</v>
+        <v>0.304</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.9589905362776026</v>
+        <v>0.3250825082508251</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4923312883435583</v>
+        <v>0.2970779220779221</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9984177215189873</v>
+        <v>0.117741935483871</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9904912836767037</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.992</v>
+        <v>0.2990353697749196</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9906103286384976</v>
+        <v>0.1550888529886914</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9907120743034056</v>
+        <v>0.3121019108280255</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9908675799086758</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9905362776025236</v>
+        <v>0.2793388429752066</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.9908116385911179</v>
+        <v>0.2957516339869281</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.9921383647798742</v>
+        <v>0.8564356435643564</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9906396255850234</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.9891304347826086</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.9886914378029079</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.990521327014218</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.9919614147909968</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.9921383647798742</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9451612903225807</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.0330188679245283</v>
+        <v>0.2878048780487805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1867283950617284</v>
+        <v>0.745928338762215</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9844961240310077</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8850931677018633</v>
+        <v>0.7591362126245847</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03715170278637771</v>
+        <v>0.7885615251299827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03803486529318542</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03641881638846738</v>
+        <v>0.004909983633387889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03271028037383177</v>
+        <v>0.1456953642384106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07886435331230283</v>
+        <v>0.2165289256198347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06031746031746032</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03235747303543914</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05164319248826291</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6047619047619047</v>
+        <v>0.17206132879046</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02572347266881029</v>
+        <v>0.2504038772213247</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2526964560862866</v>
+        <v>0.167741935483871</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1637795275590551</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8890675241157556</v>
+        <v>0.3752039151712888</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0594679186228482</v>
+        <v>0.9984</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3107692307692307</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05648854961832061</v>
+        <v>0.9967793880837359</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9607535321821036</v>
+        <v>0.9983818770226537</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9652448657187994</v>
+        <v>0.4052718286655684</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9638932496075353</v>
+        <v>0.2462809917355372</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9669811320754716</v>
+        <v>0.2453151618398637</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9680511182108626</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9412698412698413</v>
+        <v>0.2603833865814696</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6422893481717011</v>
+        <v>0.2635782747603834</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.9613601236476044</v>
+        <v>0.2549342105263158</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9639498432601881</v>
+        <v>0.2601626016260163</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.9251170046801872</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4878787878787879</v>
+        <v>0.2562814070351759</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.9674418604651163</v>
+        <v>0.1060358890701468</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9684542586750788</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9682539682539683</v>
+        <v>0.2557755775577558</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.966412213740458</v>
+        <v>0.1382636655948553</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.959375</v>
+        <v>0.2622950819672131</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9623493975903614</v>
+        <v>0.2508305647840531</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9625</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.9738058551617874</v>
+        <v>0.254180602006689</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.9636650868878357</v>
+        <v>0.8777219430485762</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9727272727272728</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.963302752293578</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.9618441971383148</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.9648562300319489</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.9307086614173228</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.9585326953748007</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.05376344086021505</v>
+        <v>0.2455284552845528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2437888198757764</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9523052464228935</v>
+        <v>0.724709784411277</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8850931677018633</v>
+        <v>0.7591362126245847</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1105919003115265</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09294871794871795</v>
+        <v>0.79421768707483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.151840490797546</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1145996860282575</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1772151898734177</v>
+        <v>0.1254180602006689</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1123595505617977</v>
+        <v>0.7408637873754153</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09968847352024922</v>
+        <v>0.8013029315960912</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0352</v>
+        <v>0.7382113821138211</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5698412698412698</v>
+        <v>0.07178631051752922</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8847352024922118</v>
+        <v>0.7340946166394779</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1009463722397476</v>
+        <v>0.1677740863787375</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2621664050235479</v>
+        <v>0.01963993453355155</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2231012658227848</v>
+        <v>0.1316239316239316</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.177257525083612</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1787974683544304</v>
+        <v>0.7536</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3657407407407408</v>
+        <v>0.1743264659270999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.115919629057187</v>
+        <v>0.764026402640264</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8962264150943396</v>
+        <v>0.8043117744610282</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8821656050955414</v>
+        <v>0.1933884297520661</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8632075471698113</v>
+        <v>0.1877076411960133</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8649921507064364</v>
+        <v>0.1843478260869565</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8807947019867549</v>
+        <v>0.1661016949152542</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8599348534201955</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6791530944625407</v>
+        <v>0.1693290734824281</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8799368088467614</v>
+        <v>0.1750405186385738</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8801261829652997</v>
+        <v>0.1837060702875399</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.8593508500772797</v>
+        <v>0.2006578947368421</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5303265940902022</v>
+        <v>0.1694630872483222</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8944881889763779</v>
+        <v>0.001631321370309951</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8781645569620253</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8745980707395499</v>
+        <v>0.1630615640599002</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8828967642526965</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8828967642526965</v>
+        <v>0.1845140032948929</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8781954887218045</v>
+        <v>0.1888701517706577</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.881619937694704</v>
+        <v>0.1621160409556314</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8950617283950617</v>
+        <v>0.1810766721044046</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.886762360446571</v>
+        <v>0.9261744966442953</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8715596330275229</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.8809160305343512</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.882258064516129</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.8670886075949367</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.8760064412238325</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.8826291079812206</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.8460291734197731</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.869701726844584</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.1286821705426357</v>
+        <v>0.1783333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5500770416024653</v>
+        <v>0.9983388704318937</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.7680921052631579</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03715170278637771</v>
+        <v>0.7885615251299827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1105919003115265</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8412698412698413</v>
+        <v>0.8324697754749568</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.008375209380234505</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9860896445131375</v>
+        <v>0.005050505050505051</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9781931464174455</v>
+        <v>0.08319467554076539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.740506329113924</v>
+        <v>0.7794361525704809</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7882534775888718</v>
+        <v>0.838160136286201</v>
       </c>
       <c r="M6" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03559322033898305</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7792642140468228</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1101836393989983</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02508361204013378</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1440823327615781</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7835218093699515</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.7969798657718121</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.837248322147651</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1943048576214405</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1203252032520325</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1059027777777778</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1188925081433225</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1109271523178808</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1144781144781145</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1258389261744967</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.1182432432432432</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.03993855606758832</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.9334389857369255</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.7445820433436533</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.5490506329113924</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1130573248407643</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.9984639016897081</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.4624808575803981</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.754601226993865</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.003125</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.003125</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.003115264797507788</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.003105590062111801</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.003210272873194221</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.0110410094637224</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.2818471337579618</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.003081664098613251</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.0046801872074883</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.01533742331288344</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.3185298621745788</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0141287284144427</v>
-      </c>
       <c r="AI6" t="n">
-        <v>0.004716981132075472</v>
+        <v>0.803082191780822</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.003179650238473768</v>
+        <v>0.1138613861386139</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.003091190108191654</v>
+        <v>0.003252032520325203</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003076923076923077</v>
+        <v>0.119327731092437</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.003003003003003003</v>
+        <v>0.117056856187291</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0046801872074883</v>
+        <v>0.09930313588850175</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.003058103975535168</v>
+        <v>0.1116666666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.928082191780822</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001506024096385542</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.004573170731707317</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.004709576138147566</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.004622496147919877</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.004724409448818898</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.02153846153846154</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.03194888178913738</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.004746835443037975</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.8531684698608965</v>
+        <v>0.1122278056951424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7452229299363057</v>
+        <v>0.7819672131147541</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01271860095389507</v>
+        <v>0.998330550918197</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03803486529318542</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09294871794871795</v>
+        <v>0.79421768707483</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8412698412698413</v>
+        <v>0.8324697754749568</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8338461538461538</v>
+        <v>0.004966887417218543</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8591772151898734</v>
+        <v>0.1216666666666667</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.1580698835274542</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.9950738916256158</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9984326018808778</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.9902912621359223</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001602564102564103</v>
+        <v>0.1211072664359862</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0427892234548336</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.900974025974026</v>
+        <v>0.1957928802588997</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7337559429477021</v>
+        <v>0.1447368421052632</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7446457990115322</v>
+        <v>0.3321917808219178</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.376271186440678</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8279742765273312</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6009615384615384</v>
+        <v>0.1793650793650794</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0.9967479674796748</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006369426751592357</v>
+        <v>0.9983471074380166</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00322061191626409</v>
+        <v>0.4082644628099174</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003205128205128205</v>
+        <v>0.1830065359477124</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.004846526655896607</v>
+        <v>0.1846153846153846</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003278688524590164</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02755267423014587</v>
+        <v>0.1926163723916533</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3937397034596375</v>
+        <v>0.1950819672131147</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.006359300476947536</v>
+        <v>0.2039800995024875</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.1934959349593496</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.04094488188976378</v>
+        <v>0.2115702479338843</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.460093896713615</v>
+        <v>0.1843003412969283</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.008090614886731391</v>
+        <v>0.08427876823338736</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.004885993485342019</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004901960784313725</v>
+        <v>0.1983606557377049</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004777070063694267</v>
+        <v>0.1127694859038143</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003110419906687403</v>
+        <v>0.1941272430668842</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.006153846153846154</v>
+        <v>0.1873963515754561</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.004792332268370607</v>
+        <v>0.1689419795221843</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.00625</v>
+        <v>0.18561872909699</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.003125</v>
+        <v>0.8892561983471075</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.006182380216383307</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.00631911532385466</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.001594896331738437</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.006289308176100629</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.004777070063694267</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.8149920255183413</v>
+        <v>0.180921052631579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5484351713859911</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01975683890577508</v>
+        <v>0.001620745542949757</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03641881638846738</v>
+        <v>0.004909983633387889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.151840490797546</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.008375209380234505</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8338461538461538</v>
+        <v>0.004966887417218543</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9655688622754491</v>
+        <v>0.0113452188006483</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.735202492211838</v>
+        <v>0.001633986928104575</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7853949329359166</v>
+        <v>0.003262642740619902</v>
       </c>
       <c r="M8" t="n">
+        <v>0.004862236628849271</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.0060790273556231</v>
-      </c>
       <c r="O8" t="n">
-        <v>0.03753753753753754</v>
+        <v>0.004885993485342019</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9195046439628483</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7291666666666666</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5438066465256798</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1544461778471139</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9954198473282443</v>
+        <v>0.001579778830963665</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4661654135338346</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7529585798816568</v>
+        <v>0.003252032520325203</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0196969696969697</v>
+        <v>0.004792332268370607</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01702786377708978</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01501501501501501</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01993865030674847</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01547987616099071</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0248062015503876</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.309748427672956</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01676829268292683</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01684532924961715</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03177004538577912</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3388305847076462</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.02887537993920973</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.01684532924961715</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0183206106870229</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01804511278195489</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02242152466367713</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0161764705882353</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.02265861027190332</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.01777777777777778</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0182370820668693</v>
+        <v>0.006633499170812604</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.01756954612005857</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.01497005988023952</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.0171875</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.02137404580152672</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.02153846153846154</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.02556390977443609</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.04665629860031104</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.01846153846153846</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.8272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5371517027863777</v>
+        <v>0.006493506493506494</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009302325581395349</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03271028037383177</v>
+        <v>0.1456953642384106</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1145996860282575</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9860896445131375</v>
+        <v>0.005050505050505051</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8591772151898734</v>
+        <v>0.1216666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9655688622754491</v>
+        <v>0.0113452188006483</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9420062695924765</v>
+        <v>0.5915032679738562</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7580128205128205</v>
+        <v>0.1525974025974026</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8012232415902141</v>
+        <v>0.1039370078740157</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001552795031055901</v>
+        <v>0.1464968152866242</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03675344563552833</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9548286604361371</v>
+        <v>0.56957928802589</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7695924764890282</v>
+        <v>0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.8413223140495868</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1141479099678457</v>
+        <v>0.7725040916530278</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9554531490015361</v>
+        <v>0.1544461778471139</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5316846986089645</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7765793528505393</v>
+        <v>0.1362179487179487</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.110223642172524</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.7161500815660685</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.537842190016103</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>0.5566666666666666</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.5469798657718121</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.5448818897637795</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2939297124600639</v>
+        <v>0.5628930817610063</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.550561797752809</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003067484662576687</v>
+        <v>0.5489566613162119</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01557632398753894</v>
+        <v>0.5339805825242718</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3065250379362671</v>
+        <v>0.5551894563426688</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.007874015748031496</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>0.1160130718954248</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.5570032573289903</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>0.9967741935483871</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>0.5392156862745098</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>0.5372168284789643</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>0.5464926590538336</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>0.01990049751243781</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.01545595054095827</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.03354632587859425</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.8792569659442725</v>
+        <v>0.5400981996726678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5296875</v>
+        <v>0.1745513866231648</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03645007923930269</v>
+        <v>0.2669902912621359</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07886435331230283</v>
+        <v>0.2165289256198347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1772151898734177</v>
+        <v>0.1254180602006689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9781931464174455</v>
+        <v>0.08319467554076539</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.1580698835274542</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9420062695924765</v>
+        <v>0.5915032679738562</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7491961414790996</v>
+        <v>0.2520193861066236</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7746031746031746</v>
+        <v>0.208130081300813</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.2467320261437909</v>
       </c>
       <c r="N10" t="n">
-        <v>0.024</v>
+        <v>0.9096989966555183</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07861635220125786</v>
+        <v>0.2245557350565428</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9024</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7309486780715396</v>
+        <v>0.5827922077922078</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5297906602254429</v>
+        <v>0.5109983079526227</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.5640599001663894</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9731012658227848</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4463722397476341</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7611710323574731</v>
+        <v>0.2283849918433931</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03442879499217527</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03365384615384615</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02821316614420063</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03761755485893417</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.03089430894308943</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0468497576736672</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3128038897893031</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.03475513428120063</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03715170278637771</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.05015673981191222</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3323076923076923</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.04423380726698262</v>
+        <v>0.6332794830371568</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0336</v>
+        <v>0.2363636363636364</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0275974025974026</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.032</v>
+        <v>0.6360655737704918</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0359375</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.03474320241691843</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.03448275862068965</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03421461897356143</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.1503378378378378</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0289193302891933</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.03072196620583717</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.0322061191626409</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.03508771929824561</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.03709677419354838</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.05696202531645569</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.05617977528089887</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.03486529318541997</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.8053375196232339</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8515625</v>
+        <v>0.7287581699346405</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0420032310177706</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06031746031746032</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1123595505617977</v>
+        <v>0.7408637873754153</v>
       </c>
       <c r="F11" t="n">
-        <v>0.740506329113924</v>
+        <v>0.7794361525704809</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.9950738916256158</v>
       </c>
       <c r="H11" t="n">
-        <v>0.735202492211838</v>
+        <v>0.001633986928104575</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7580128205128205</v>
+        <v>0.1525974025974026</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7491961414790996</v>
+        <v>0.2520193861066236</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9967948717948718</v>
+        <v>0.9983498349834984</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01143790849673203</v>
+        <v>0.1966666666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.995114006514658</v>
       </c>
       <c r="P11" t="n">
-        <v>0.814935064935065</v>
+        <v>0.2845659163987138</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6704180064308681</v>
+        <v>0.1682847896440129</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8491803278688524</v>
+        <v>0.342327150084317</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1180327868852459</v>
+        <v>0.3862520458265139</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7313915857605178</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7133757961783439</v>
+        <v>0.2794348508634223</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.9919224555735057</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03503184713375796</v>
+        <v>0.9934533551554828</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03927986906710311</v>
+        <v>0.4337748344370861</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03481012658227848</v>
+        <v>0.2756849315068493</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03826955074875208</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.06188925081433225</v>
+        <v>0.2943037974683544</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4248366013071895</v>
+        <v>0.3014586709886548</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.04088050314465409</v>
+        <v>0.3014827018121911</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.03349282296650718</v>
+        <v>0.2912</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.07234726688102894</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5574803149606299</v>
+        <v>0.2833607907742998</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.1062091503267974</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.03902439024390244</v>
+        <v>0.9932885906040269</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.03150912106135987</v>
+        <v>0.2920065252854813</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.03536977491961415</v>
+        <v>0.1506410256410256</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03164556962025317</v>
+        <v>0.3037156704361874</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.03852080123266564</v>
+        <v>0.2773246329526917</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.2628865979381443</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.03416149068322982</v>
+        <v>0.2911184210526316</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0368</v>
+        <v>0.8631051752921536</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.03426791277258567</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.03827751196172249</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.02295081967213115</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.03745928338762215</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.03618421052631579</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.05414012738853503</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.09634551495016612</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.04045307443365696</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.7733755942947702</v>
+        <v>0.2887096774193548</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8091603053435115</v>
+        <v>0.7907348242811502</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02311248073959938</v>
+        <v>0.9984</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03235747303543914</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09968847352024922</v>
+        <v>0.8013029315960912</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7882534775888718</v>
+        <v>0.838160136286201</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9984326018808778</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7853949329359166</v>
+        <v>0.003262642740619902</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8012232415902141</v>
+        <v>0.1039370078740157</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7746031746031746</v>
+        <v>0.208130081300813</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9967948717948718</v>
+        <v>0.9983498349834984</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.9937205651491365</v>
       </c>
       <c r="N12" t="n">
-        <v>0.001584786053882726</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03846153846153846</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8730407523510971</v>
+        <v>0.2455284552845528</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.1069182389937107</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.2753378378378378</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1073170731707317</v>
+        <v>0.3312</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7850467289719626</v>
+        <v>0.9984152139461173</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6897081413210445</v>
+        <v>0.2419106317411402</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0140625</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01574803149606299</v>
+        <v>0.3569131832797428</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.01253918495297806</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0143312101910828</v>
+        <v>0.2478920741989882</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.02978056426332288</v>
+        <v>0.2603833865814696</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3824959481361426</v>
+        <v>0.2496</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0184331797235023</v>
+        <v>0.2580128205128205</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01410658307210031</v>
+        <v>0.2576</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0444104134762634</v>
+        <v>0.2734761120263591</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.4854517611026034</v>
+        <v>0.2483552631578947</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.02047244094488189</v>
+        <v>0.06006493506493506</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.01569858712715855</v>
+        <v>0.9983660130718954</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01271860095389507</v>
+        <v>0.2430213464696223</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01555209953343701</v>
+        <v>0.1061093247588424</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.009202453987730062</v>
+        <v>0.2681744749596123</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.01506024096385542</v>
+        <v>0.2451298701298701</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01547987616099071</v>
+        <v>0.2243150684931507</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01671732522796352</v>
+        <v>0.2536585365853659</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01564945226917058</v>
+        <v>0.9055374592833876</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01374045801526718</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.0182370820668693</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.01102362204724409</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.0171606864274571</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.01587301587301587</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.02439024390243903</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.01567398119122257</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.8133748055987559</v>
+        <v>0.2312703583061889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.7245222929936306</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04458598726114649</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05164319248826291</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0352</v>
+        <v>0.7382113821138211</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.9902912621359223</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.004862236628849271</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001552795031055901</v>
+        <v>0.1464968152866242</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.2467320261437909</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.9937205651491365</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5078864353312302</v>
+        <v>0.1880064829821718</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05590062111801242</v>
+        <v>0.995260663507109</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.2791068580542265</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01866251944012442</v>
+        <v>0.1712</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.3532338308457711</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03409090909090909</v>
+        <v>0.3932038834951456</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.9905808477237049</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.2685887708649469</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.985691573926868</v>
       </c>
       <c r="W13" t="n">
-        <v>0.05039370078740157</v>
+        <v>0.9888178913738019</v>
       </c>
       <c r="X13" t="n">
-        <v>0.05371248025276461</v>
+        <v>0.434991974317817</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.05238095238095238</v>
+        <v>0.2739059967585089</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.048</v>
+        <v>0.2679738562091503</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04426229508196721</v>
+        <v>0.2821782178217822</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0380952380952381</v>
+        <v>0.2817337461300309</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02258064516129032</v>
+        <v>0.2884310618066561</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0550314465408805</v>
+        <v>0.2873376623376623</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.05079365079365079</v>
+        <v>0.2802547770700637</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0390625</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.284329563812601</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.04983922829581994</v>
+        <v>0.106687898089172</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.04133545310015898</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.05348460291734198</v>
+        <v>0.2875605815831987</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04610492845786963</v>
+        <v>0.1480891719745223</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04866562009419152</v>
+        <v>0.2937399678972712</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.05513016845329249</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.04416403785488959</v>
+        <v>0.2595041322314049</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.05084745762711865</v>
+        <v>0.2781350482315113</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.8629690048939641</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.04747320061255743</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.04636785162287481</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.06022187004754358</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.05039370078740157</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.04313099041533546</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.04821150855365474</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.04383116883116883</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.03709677419354838</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
+        <v>0.2669826224328594</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08722741433021806</v>
+        <v>0.09951060358890701</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6253968253968254</v>
+        <v>0.1996699669966997</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6047619047619047</v>
+        <v>0.17206132879046</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5698412698412698</v>
+        <v>0.07178631051752922</v>
       </c>
       <c r="F14" t="n">
+        <v>0.03559322033898305</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1211072664359862</v>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.001602564102564103</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0060790273556231</v>
-      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="J14" t="n">
-        <v>0.024</v>
+        <v>0.9096989966555183</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01143790849673203</v>
+        <v>0.1966666666666667</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001584786053882726</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5078864353312302</v>
+        <v>0.1880064829821718</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.609105180533752</v>
+        <v>0.1737704918032787</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00322061191626409</v>
+        <v>0.8270181219110379</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1181102362204724</v>
+        <v>0.7278797996661102</v>
       </c>
       <c r="R14" t="n">
-        <v>0.07496012759170653</v>
+        <v>0.5949152542372881</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5594855305466238</v>
+        <v>0.6270903010033445</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01109350237717908</v>
+        <v>0.1655844155844156</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1656050955414013</v>
+        <v>0.8449367088607594</v>
       </c>
       <c r="V14" t="n">
-        <v>0.009419152276295133</v>
+        <v>0.1752921535893155</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6442006269592476</v>
+        <v>0.1330049261083744</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6266025641025641</v>
+        <v>0.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6412698412698413</v>
+        <v>0.8306188925081434</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6353503184713376</v>
+        <v>0.8505154639175257</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6143790849673203</v>
+        <v>0.8304794520547946</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5922330097087378</v>
+        <v>0.8387622149837134</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3793677204658902</v>
+        <v>0.8370967741935483</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.631496062992126</v>
+        <v>0.8528428093645485</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6419558359621451</v>
+        <v>0.8459016393442623</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.6040688575899843</v>
+        <v>0.8360927152317881</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3085443037974683</v>
+        <v>0.8647746243739566</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.6463022508038585</v>
+        <v>0.8218954248366013</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.6220095693779905</v>
+        <v>0.17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.60828025477707</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.6349453978159126</v>
+        <v>0.7933884297520661</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.6697674418604651</v>
+        <v>0.8441127694859039</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.6621004566210046</v>
+        <v>0.8511705685618729</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.6311605723370429</v>
+        <v>0.8687392055267703</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.6217054263565891</v>
+        <v>0.8431703204047217</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.6141732283464567</v>
+        <v>0.09661016949152543</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.6321483771251932</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.6191950464396285</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.7186495176848875</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.606973058637084</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.5984</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.616822429906542</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.5970636215334421</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.6340288924558587</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.007936507936507936</v>
+        <v>0.8590381426202321</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1829457364341085</v>
+        <v>0.7207062600321027</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9796875</v>
+        <v>0.9983844911147012</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8847352024922118</v>
+        <v>0.7340946166394779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03993855606758832</v>
+        <v>0.7792642140468228</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0427892234548336</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03753753753753754</v>
+        <v>0.004885993485342019</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03675344563552833</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07861635220125786</v>
+        <v>0.2245557350565428</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.995114006514658</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03846153846153846</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05590062111801242</v>
+        <v>0.995260663507109</v>
       </c>
       <c r="N15" t="n">
-        <v>0.609105180533752</v>
+        <v>0.1737704918032787</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03015873015873016</v>
+        <v>0.2613636363636364</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2526964560862866</v>
+        <v>0.1887096774193548</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1757188498402556</v>
+        <v>0.3727422003284072</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8871224165341812</v>
+        <v>0.4016260162601626</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06386292834890965</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3091190108191654</v>
+        <v>0.2492260061919505</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06717557251908397</v>
+        <v>0.9952456418383518</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9581395348837209</v>
+        <v>0.9967689822294022</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9603174603174603</v>
+        <v>0.4294975688816856</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9627329192546584</v>
+        <v>0.2528363047001621</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9625</v>
+        <v>0.2445561139028476</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9627228525121556</v>
+        <v>0.2572402044293015</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9382911392405063</v>
+        <v>0.2740384615384616</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.6427432216905901</v>
+        <v>0.2678288431061807</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.2638436482084691</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.9620853080568721</v>
+        <v>0.2614896988906498</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.9192546583850931</v>
+        <v>0.2796747967479675</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.4773413897280967</v>
+        <v>0.2537067545304778</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.9671361502347418</v>
+        <v>0.113452188006483</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.9637223974763407</v>
+        <v>0.9966722129783694</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.2624798711755233</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.963302752293578</v>
+        <v>0.1601307189542484</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.9548286604361371</v>
+        <v>0.2669902912621359</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.9578947368421052</v>
+        <v>0.2552845528455285</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.9582689335394127</v>
+        <v>0.2354892205638474</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.247557003257329</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.9595015576323987</v>
+        <v>0.8606965174129353</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.9700149925037481</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.9585253456221198</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.9587955625990491</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.9594383775351014</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.9603803486529319</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.9418238993710691</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.9544025157232704</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.05909797822706065</v>
+        <v>0.2507987220447284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.634375</v>
+        <v>0.2163461538461539</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0064</v>
+        <v>0.2987220447284345</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02572347266881029</v>
+        <v>0.2504038772213247</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1009463722397476</v>
+        <v>0.1677740863787375</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9334389857369255</v>
+        <v>0.1101836393989983</v>
       </c>
       <c r="G16" t="n">
-        <v>0.900974025974026</v>
+        <v>0.1957928802588997</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9195046439628483</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9548286604361371</v>
+        <v>0.56957928802589</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9024</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.814935064935065</v>
+        <v>0.2845659163987138</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8730407523510971</v>
+        <v>0.2455284552845528</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.2791068580542265</v>
       </c>
       <c r="N16" t="n">
-        <v>0.00322061191626409</v>
+        <v>0.8270181219110379</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03015873015873016</v>
+        <v>0.2613636363636364</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0.5712</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6326860841423948</v>
+        <v>0.5215231788079471</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1006493506493507</v>
+        <v>0.5779220779220779</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8977987421383647</v>
+        <v>0.25625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5377358490566038</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8460342146189735</v>
+        <v>0.2721417069243156</v>
       </c>
       <c r="W16" t="n">
-        <v>0.004769475357710651</v>
+        <v>0.2255520504731861</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0016</v>
+        <v>0.5958132045088567</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.003164556962025316</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.003174603174603175</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.00165016501650165</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01132686084142395</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.3130148270181219</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004784688995215311</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.006349206349206349</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0141287284144427</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.6089743589743589</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.003189792663476874</v>
+        <v>0.2719734660033167</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.003311258278145695</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.00315955766192733</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.004672897196261682</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.004622496147919877</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.00473186119873817</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.004629629629629629</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0032</v>
+        <v>0.2042833607907743</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.00310077519379845</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.004658385093167702</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.004830917874396135</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.004784688995215311</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.01572327044025157</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.03079416531604538</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0.003225806451612903</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.9589257503949447</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5579598145285936</v>
+        <v>0.01615508885298869</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2110236220472441</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2526964560862866</v>
+        <v>0.167741935483871</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2621664050235479</v>
+        <v>0.01963993453355155</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7445820433436533</v>
+        <v>0.02508361204013378</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7337559429477021</v>
+        <v>0.1447368421052632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7291666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7695924764890282</v>
+        <v>0.9792</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7309486780715396</v>
+        <v>0.5827922077922078</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6704180064308681</v>
+        <v>0.1682847896440129</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.1069182389937107</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01866251944012442</v>
+        <v>0.1712</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1181102362204724</v>
+        <v>0.7278797996661102</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2526964560862866</v>
+        <v>0.1887096774193548</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0.5712</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5633802816901409</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2667731629392971</v>
+        <v>0.9183006535947712</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7310664605873262</v>
+        <v>0.1808176100628931</v>
       </c>
       <c r="U17" t="n">
-        <v>0.499219968798752</v>
+        <v>0.5300462249614792</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7083969465648855</v>
+        <v>0.1562998405103668</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1925465838509317</v>
+        <v>0.1310679611650485</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1930379746835443</v>
+        <v>0.8543371522094927</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.196319018404908</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1993817619783617</v>
+        <v>0.5488215488215489</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.1926751592356688</v>
+        <v>0.555</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1932367149758454</v>
+        <v>0.5583596214511041</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4278846153846154</v>
+        <v>0.5584</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.2073732718894009</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.196594427244582</v>
+        <v>0.5431309904153354</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1829457364341085</v>
+        <v>0.5326797385620915</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.3770992366412214</v>
+        <v>0.5635451505016722</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1874015748031496</v>
+        <v>0.9556259904912837</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1871069182389937</v>
+        <v>0.1405228758169935</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2103559870550162</v>
+        <v>0.5528846153846154</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.1947040498442368</v>
+        <v>0.967479674796748</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.1826625386996904</v>
+        <v>0.5463414634146342</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.2018209408194234</v>
+        <v>0.5387096774193548</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.1918876755070203</v>
+        <v>0.5440931780366056</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.1972477064220184</v>
+        <v>0.5548281505728314</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.196875</v>
+        <v>0.04597701149425287</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.2006079027355623</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.1931993817619784</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.1844197138314785</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.2044025157232705</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.1894904458598726</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.2194744976816074</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.2304</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.196875</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0.7864823348694316</v>
+        <v>0.5571658615136876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9829192546583851</v>
+        <v>0.1231527093596059</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.3674496644295302</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1637795275590551</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2231012658227848</v>
+        <v>0.1316239316239316</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5490506329113924</v>
+        <v>0.1440823327615781</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7446457990115322</v>
+        <v>0.3321917808219178</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5438066465256798</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.8413223140495868</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5297906602254429</v>
+        <v>0.5109983079526227</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8491803278688524</v>
+        <v>0.342327150084317</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.2753378378378378</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.3532338308457711</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07496012759170653</v>
+        <v>0.5949152542372881</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1757188498402556</v>
+        <v>0.3727422003284072</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6326860841423948</v>
+        <v>0.5215231788079471</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5633802816901409</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2203672787979967</v>
+        <v>0.9983333333333333</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5632</v>
+        <v>0.3680781758957655</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8753943217665615</v>
+        <v>0.4715189873417722</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8323076923076923</v>
+        <v>0.3322314049586777</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1526232114467408</v>
+        <v>0.3262642740619902</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.9394957983193277</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1325878594249201</v>
+        <v>0.4861337683523654</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1396825396825397</v>
+        <v>0.4786324786324787</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1556291390728477</v>
+        <v>0.4982578397212544</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1847649918962723</v>
+        <v>0.4975767366720517</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5048231511254019</v>
+        <v>0.5024390243902439</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1473354231974922</v>
+        <v>0.4983333333333334</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1640378548895899</v>
+        <v>0.4942339373970346</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2074303405572755</v>
+        <v>0.4792013311148087</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.6992248062015504</v>
+        <v>0.5126050420168067</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1414790996784566</v>
+        <v>0.7926421404682275</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.1572123176661264</v>
+        <v>0.3310924369747899</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1598023064250412</v>
+        <v>0.4933110367892977</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.1560509554140127</v>
+        <v>0.8286189683860233</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.1563467492260062</v>
+        <v>0.480865224625624</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.1598173515981735</v>
+        <v>0.4822335025380711</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.1576433121019108</v>
+        <v>0.4715025906735751</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.1599378881987578</v>
+        <v>0.4875207986688852</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.1518578352180937</v>
+        <v>0.1942078364565588</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.1496913580246914</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.162754303599374</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.1375404530744337</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.1696574225122349</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.168503937007874</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.224390243902439</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.1515151515151515</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0.7338582677165354</v>
+        <v>0.4917218543046358</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2376395534290271</v>
+        <v>0.1636952998379254</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9546191247974068</v>
+        <v>0.4121510673234811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8890675241157556</v>
+        <v>0.3752039151712888</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.177257525083612</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1130573248407643</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.376271186440678</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1544461778471139</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1141479099678457</v>
+        <v>0.7725040916530278</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.5640599001663894</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1180327868852459</v>
+        <v>0.3862520458265139</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1073170731707317</v>
+        <v>0.3312</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03409090909090909</v>
+        <v>0.3932038834951456</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5594855305466238</v>
+        <v>0.6270903010033445</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8871224165341812</v>
+        <v>0.4016260162601626</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1006493506493507</v>
+        <v>0.5779220779220779</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2667731629392971</v>
+        <v>0.9183006535947712</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2203672787979967</v>
+        <v>0.9983333333333333</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1784565916398714</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3610223642172524</v>
+        <v>0.5388198757763976</v>
       </c>
       <c r="V19" t="n">
-        <v>0.127591706539075</v>
+        <v>0.3915857605177994</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.3600654664484452</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8832</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.8621236133122029</v>
+        <v>0.5367047308319739</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.8615635179153095</v>
+        <v>0.5329949238578681</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.5734265734265734</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8655737704918033</v>
+        <v>0.5638977635782748</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.5375626043405676</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.8835725677830941</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.8788368336025848</v>
+        <v>0.5711974110032363</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.8608</v>
+        <v>0.543801652892562</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.5621890547263682</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.8896103896103896</v>
+        <v>0.71875</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.8782467532467533</v>
+        <v>0.3668341708542713</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.8770226537216829</v>
+        <v>0.5475409836065573</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.8812199036918138</v>
+        <v>0.7637540453074434</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.8804523424878837</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.8767550702028081</v>
+        <v>0.5473856209150327</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.8806451612903226</v>
+        <v>0.537542662116041</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8954041204437401</v>
+        <v>0.5508196721311476</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.887459807073955</v>
+        <v>0.2345058626465662</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.8711180124223602</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.8760064412238325</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0.8856682769726248</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.8661290322580645</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.8778501628664495</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.8857589984350548</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.8590381426202321</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.8701923076923077</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0.1233974358974359</v>
+        <v>0.5598006644518272</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.575</v>
+        <v>0.7430340557275542</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02369668246445497</v>
+        <v>0.9984152139461173</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0594679186228482</v>
+        <v>0.9984</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1787974683544304</v>
+        <v>0.7536</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9984639016897081</v>
+        <v>0.7835218093699515</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8279742765273312</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9954198473282443</v>
+        <v>0.001579778830963665</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9554531490015361</v>
+        <v>0.1544461778471139</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9731012658227848</v>
+        <v>0.217741935483871</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7313915857605178</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7850467289719626</v>
+        <v>0.9984152139461173</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.9905808477237049</v>
       </c>
       <c r="N20" t="n">
-        <v>0.01109350237717908</v>
+        <v>0.1655844155844156</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06386292834890965</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8977987421383647</v>
+        <v>0.25625</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7310664605873262</v>
+        <v>0.1808176100628931</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5632</v>
+        <v>0.3680781758957655</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1784565916398714</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4868624420401855</v>
+        <v>0.2481315396113603</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.9984301412872841</v>
       </c>
       <c r="W20" t="n">
-        <v>0.02515723270440252</v>
+        <v>0.9984202211690363</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02543720190779014</v>
+        <v>0.4497607655502392</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.02190923317683881</v>
+        <v>0.2468553459119497</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.03149606299212598</v>
+        <v>0.2411003236245955</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.02103559870550162</v>
+        <v>0.2568659127625202</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.03662420382165605</v>
+        <v>0.2649310872894334</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3135048231511254</v>
+        <v>0.2695252679938744</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.02472952086553323</v>
+        <v>0.2683307332293292</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0282574568288854</v>
+        <v>0.2635658914728682</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0375</v>
+        <v>0.2744479495268139</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.3574730354391371</v>
+        <v>0.2551505546751189</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.03662420382165605</v>
+        <v>0.1095461658841941</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.02834645669291339</v>
+        <v>0.9952</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.02568218298555377</v>
+        <v>0.2610062893081761</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.01901743264659271</v>
+        <v>0.1507936507936508</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.02821316614420063</v>
+        <v>0.2605304212168487</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.02413273001508296</v>
+        <v>0.254746835443038</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.03322784810126582</v>
+        <v>0.2320261437908497</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.02476780185758514</v>
+        <v>0.2567353407290016</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.02830188679245283</v>
+        <v>0.8675282714054927</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.0258751902587519</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.02469135802469136</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.02243589743589744</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.0297339593114241</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.02889245585874799</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.04205607476635514</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.06220095693779904</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0.02702702702702703</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0.8287037037037037</v>
+        <v>0.242472266244057</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0.2159264931087289</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3006230529595015</v>
+        <v>0.2904689863842663</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3107692307692307</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3657407407407408</v>
+        <v>0.1743264659270999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4624808575803981</v>
+        <v>0.1123595505617977</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6009615384615384</v>
+        <v>0.1793650793650794</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4661654135338346</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5316846986089645</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4463722397476341</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7133757961783439</v>
+        <v>0.2794348508634223</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6897081413210445</v>
+        <v>0.2419106317411402</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.2685887708649469</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1656050955414013</v>
+        <v>0.8449367088607594</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3091190108191654</v>
+        <v>0.2492260061919505</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5377358490566038</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.499219968798752</v>
+        <v>0.5300462249614792</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8753943217665615</v>
+        <v>0.4715189873417722</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3610223642172524</v>
+        <v>0.5388198757763976</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4868624420401855</v>
+        <v>0.2481315396113603</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6957186544342507</v>
+        <v>0.2592024539877301</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3</v>
+        <v>0.2259541984732824</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3139717425431711</v>
+        <v>0.5579598145285936</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2639751552795031</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.2753164556962026</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.3070739549839228</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.3280254777070064</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5598705501618123</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.3020030816640986</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.3001555209953344</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.3569230769230769</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.9241486068111455</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.2892690513219285</v>
+        <v>0.5751533742331288</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.3034591194968553</v>
+        <v>0.2590266875981161</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.3039370078740157</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.3129890453834116</v>
+        <v>0.573394495412844</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.2896764252696456</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.3070044709388972</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.3059006211180124</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.2974203338391502</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.293103448275862</v>
+        <v>0.1874015748031496</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.2861491628614916</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.3134556574923548</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.2750397456279809</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.2877358490566038</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.307936507936508</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.3656597774244833</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.3037974683544304</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.6594761171032357</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.82642089093702</v>
+        <v>0.7633228840125392</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04037267080745342</v>
+        <v>0.9936406995230525</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05648854961832061</v>
+        <v>0.9967793880837359</v>
       </c>
       <c r="E22" t="n">
-        <v>0.115919629057187</v>
+        <v>0.764026402640264</v>
       </c>
       <c r="F22" t="n">
-        <v>0.754601226993865</v>
+        <v>0.7969798657718121</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.9967479674796748</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7529585798816568</v>
+        <v>0.003252032520325203</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7765793528505393</v>
+        <v>0.1362179487179487</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7611710323574731</v>
+        <v>0.2283849918433931</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.9919224555735057</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.985691573926868</v>
       </c>
       <c r="N22" t="n">
-        <v>0.009419152276295133</v>
+        <v>0.1752921535893155</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06717557251908397</v>
+        <v>0.9952456418383518</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8460342146189735</v>
+        <v>0.2721417069243156</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7083969465648855</v>
+        <v>0.1562998405103668</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8323076923076923</v>
+        <v>0.3322314049586777</v>
       </c>
       <c r="S22" t="n">
-        <v>0.127591706539075</v>
+        <v>0.3915857605177994</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.9984301412872841</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6957186544342507</v>
+        <v>0.2592024539877301</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.03389830508474576</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0.03720930232558139</v>
+        <v>0.4258373205741627</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.02153846153846154</v>
+        <v>0.2605177993527508</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.03379416282642089</v>
+        <v>0.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.04140127388535032</v>
+        <v>0.2601351351351351</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.0625</v>
+        <v>0.2751572327044025</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.426984126984127</v>
+        <v>0.273015873015873</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.03828483920367534</v>
+        <v>0.2795527156549521</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.03828483920367534</v>
+        <v>0.2733017377567141</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.07022900763358779</v>
+        <v>0.2908496732026144</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.5299401197604791</v>
+        <v>0.2612179487179487</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.03255813953488372</v>
+        <v>0.09807073954983923</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.0352760736196319</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.2673107890499195</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.03442879499217527</v>
+        <v>0.1374407582938389</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.03167420814479638</v>
+        <v>0.2731629392971246</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.03582089552238806</v>
+        <v>0.2619808306709265</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.03215926493108729</v>
+        <v>0.2471358428805237</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.03338391502276176</v>
+        <v>0.2625607779578606</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.02945736434108527</v>
+        <v>0.8962108731466227</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.03288490284005979</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.03469079939668175</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.02034428794992175</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.03400309119010819</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.03149606299212598</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0.0453857791225416</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0.08253968253968254</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.034375</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0.7914110429447853</v>
+        <v>0.2536824877250409</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1715610510046368</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9607535321821036</v>
+        <v>0.9983818770226537</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8962264150943396</v>
+        <v>0.8043117744610282</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003125</v>
+        <v>0.837248322147651</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006369426751592357</v>
+        <v>0.9983471074380166</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0196969696969697</v>
+        <v>0.004792332268370607</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.110223642172524</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03442879499217527</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="K23" t="n">
-        <v>0.03503184713375796</v>
+        <v>0.9934533551554828</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0140625</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05039370078740157</v>
+        <v>0.9888178913738019</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6442006269592476</v>
+        <v>0.1330049261083744</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9581395348837209</v>
+        <v>0.9967689822294022</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004769475357710651</v>
+        <v>0.2255520504731861</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1925465838509317</v>
+        <v>0.1310679611650485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1526232114467408</v>
+        <v>0.3262642740619902</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.3600654664484452</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02515723270440252</v>
+        <v>0.9984202211690363</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3</v>
+        <v>0.2259541984732824</v>
       </c>
       <c r="V23" t="n">
-        <v>0.03389830508474576</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0.3642172523961661</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.2368839427662957</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>0.216887417218543</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.9984025559105432</v>
+        <v>0.2371475953565506</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.9792993630573248</v>
+        <v>0.2304075235109718</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.2354788069073783</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>0.2290322580645161</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.996875</v>
+        <v>0.2318611987381703</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.9671361502347418</v>
+        <v>0.2553542009884679</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.4784615384615384</v>
+        <v>0.2255389718076285</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.9888535031847133</v>
+        <v>0.07532051282051282</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>0.9983579638752053</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>0.232</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
+        <v>0.1136</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>0.2371794871794872</v>
       </c>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>0.2302631578947368</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0.2157190635451505</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0.226904376012966</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0.9208400646203554</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0.9797191887675507</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0.9406099518459069</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.0249221183800623</v>
+        <v>0.2080645161290323</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1796875</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9904458598726115</v>
+        <v>0.4446254071661238</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9652448657187994</v>
+        <v>0.4052718286655684</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8821656050955414</v>
+        <v>0.1933884297520661</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003125</v>
+        <v>0.1943048576214405</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00322061191626409</v>
+        <v>0.4082644628099174</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01702786377708978</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.7161500815660685</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03365384615384615</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03927986906710311</v>
+        <v>0.4337748344370861</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01574803149606299</v>
+        <v>0.3569131832797428</v>
       </c>
       <c r="M24" t="n">
-        <v>0.05371248025276461</v>
+        <v>0.434991974317817</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6266025641025641</v>
+        <v>0.62</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9603174603174603</v>
+        <v>0.4294975688816856</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0016</v>
+        <v>0.5958132045088567</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1930379746835443</v>
+        <v>0.8543371522094927</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.9394957983193277</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8832</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.02543720190779014</v>
+        <v>0.4497607655502392</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3139717425431711</v>
+        <v>0.5579598145285936</v>
       </c>
       <c r="V24" t="n">
-        <v>0.03720930232558139</v>
+        <v>0.4258373205741627</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0.3642172523961661</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.9968203497615262</v>
+        <v>0.5605815831987075</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.998371335504886</v>
+        <v>0.5915254237288136</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.974025974025974</v>
+        <v>0.5866454689984102</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6168831168831169</v>
+        <v>0.5936</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>0.5862619808306709</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.5955056179775281</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.9541139240506329</v>
+        <v>0.5725938009787929</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.4720496894409938</v>
+        <v>0.5837479270315091</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.9887459807073955</v>
+        <v>0.6618357487922706</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0.3951219512195122</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>0.5849673202614379</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>0.7016129032258065</v>
       </c>
       <c r="AL24" t="n">
-        <v>1</v>
+        <v>0.568659127625202</v>
       </c>
       <c r="AM24" t="n">
-        <v>1</v>
+        <v>0.567479674796748</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0.5641891891891891</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0.5781758957654723</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>0.2627257799671593</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.9795597484276729</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0.9453376205787781</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.02511773940345369</v>
+        <v>0.5890850722311396</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9937205651491365</v>
+        <v>0.2898550724637681</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9638932496075353</v>
+        <v>0.2462809917355372</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8632075471698113</v>
+        <v>0.1877076411960133</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003115264797507788</v>
+        <v>0.1203252032520325</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003205128205128205</v>
+        <v>0.1830065359477124</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01501501501501501</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.537842190016103</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02821316614420063</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05238095238095238</v>
+        <v>0.2739059967585089</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6412698412698413</v>
+        <v>0.8306188925081434</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9627329192546584</v>
+        <v>0.2528363047001621</v>
       </c>
       <c r="P25" t="n">
-        <v>0.003164556962025316</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.196319018404908</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1325878594249201</v>
+        <v>0.4861337683523654</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8621236133122029</v>
+        <v>0.5367047308319739</v>
       </c>
       <c r="T25" t="n">
-        <v>0.02190923317683881</v>
+        <v>0.2468553459119497</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2639751552795031</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>0.02153846153846154</v>
+        <v>0.2605177993527508</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.2368839427662957</v>
       </c>
       <c r="X25" t="n">
-        <v>0.9968203497615262</v>
+        <v>0.5605815831987075</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.9968895800933126</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.9967373572593801</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.9774557165861514</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6086956521739131</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.9969040247678018</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.9952904238618524</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.9572107765451664</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.4495412844036697</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.9984301412872841</v>
+        <v>0.5836012861736335</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.9968798751950078</v>
+        <v>0.2719869706840391</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.9967637540453075</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.9968553459119497</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.9969135802469136</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.996996996996997</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.9968847352024922</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.9969325153374233</v>
+        <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.9984177215189873</v>
+        <v>0.2094155844155844</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.9968992248062015</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.9969230769230769</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.9968152866242038</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.9968404423380727</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.9983974358974359</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.9796557120500783</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0.9421221864951769</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.9968503937007874</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.02018633540372671</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1472868217054264</v>
+        <v>0.23</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9904912836767037</v>
+        <v>0.2840531561461794</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9669811320754716</v>
+        <v>0.2453151618398637</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8649921507064364</v>
+        <v>0.1843478260869565</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003105590062111801</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="G26" t="n">
-        <v>0.004846526655896607</v>
+        <v>0.1846153846153846</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01993865030674847</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.5566666666666666</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03761755485893417</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.03481012658227848</v>
+        <v>0.2756849315068493</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01253918495297806</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M26" t="n">
-        <v>0.048</v>
+        <v>0.2679738562091503</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6353503184713376</v>
+        <v>0.8505154639175257</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9625</v>
+        <v>0.2445561139028476</v>
       </c>
       <c r="P26" t="n">
-        <v>0.003174603174603175</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1993817619783617</v>
+        <v>0.5488215488215489</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1396825396825397</v>
+        <v>0.4786324786324787</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8615635179153095</v>
+        <v>0.5329949238578681</v>
       </c>
       <c r="T26" t="n">
-        <v>0.03149606299212598</v>
+        <v>0.2411003236245955</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2753164556962026</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>0.03379416282642089</v>
+        <v>0.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>0.216887417218543</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.9968895800933126</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.9983818770226537</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.9775641025641025</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6119162640901772</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.9953632148377125</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.960691823899371</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.4530046224961479</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.987460815047022</v>
+        <v>0.587248322147651</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>0.2568965517241379</v>
       </c>
       <c r="AJ26" t="n">
         <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0.5827702702702703</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -4580,584 +3964,488 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0.2050847457627119</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0.9844961240310077</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0.946515397082658</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0.0170015455950541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.171474358974359</v>
+        <v>0.2067226890756302</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9904306220095693</v>
+        <v>0.2974789915966387</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9680511182108626</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8807947019867549</v>
+        <v>0.1661016949152542</v>
       </c>
       <c r="F27" t="n">
-        <v>0.003210272873194221</v>
+        <v>0.1059027777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>0.003278688524590164</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01547987616099071</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.5469798657718121</v>
       </c>
       <c r="J27" t="n">
-        <v>0.03089430894308943</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.03826955074875208</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0143312101910828</v>
+        <v>0.2478920741989882</v>
       </c>
       <c r="M27" t="n">
-        <v>0.04426229508196721</v>
+        <v>0.2821782178217822</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6143790849673203</v>
+        <v>0.8304794520547946</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9627228525121556</v>
+        <v>0.2572402044293015</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00165016501650165</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1926751592356688</v>
+        <v>0.555</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1556291390728477</v>
+        <v>0.4982578397212544</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.5734265734265734</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02103559870550162</v>
+        <v>0.2568659127625202</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3070739549839228</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>0.04140127388535032</v>
+        <v>0.2601351351351351</v>
       </c>
       <c r="W27" t="n">
-        <v>0.9984025559105432</v>
+        <v>0.2371475953565506</v>
       </c>
       <c r="X27" t="n">
-        <v>0.998371335504886</v>
+        <v>0.5915254237288136</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.9967373572593801</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.9983818770226537</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.9966887417218543</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6184873949579832</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.9967845659163987</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.9967532467532467</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.4588607594936709</v>
+        <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.9901477832512315</v>
+        <v>0.5785953177257525</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.9983606557377049</v>
+        <v>0.2766323024054983</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.9983579638752053</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.9984101748807631</v>
+        <v>0.59</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.998468606431853</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="n">
         <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.9984025559105432</v>
+        <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.9984</v>
+        <v>0.1907216494845361</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.9984399375975039</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.9984076433121019</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.9983277591973244</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.99836867862969</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0.9983552631578947</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0.9823434991974318</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0.9586776859504132</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0.02898550724637681</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1984126984126984</v>
+        <v>0.2192429022082019</v>
       </c>
       <c r="C28" t="n">
-        <v>0.971107544141252</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9412698412698413</v>
+        <v>0.2603833865814696</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8599348534201955</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0110410094637224</v>
+        <v>0.1188925081433225</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02755267423014587</v>
+        <v>0.1926163723916533</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0248062015503876</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.5448818897637795</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0468497576736672</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0.06188925081433225</v>
+        <v>0.2943037974683544</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02978056426332288</v>
+        <v>0.2603833865814696</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0380952380952381</v>
+        <v>0.2817337461300309</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5922330097087378</v>
+        <v>0.8387622149837134</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9382911392405063</v>
+        <v>0.2740384615384616</v>
       </c>
       <c r="P28" t="n">
-        <v>0.01132686084142395</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1932367149758454</v>
+        <v>0.5583596214511041</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1847649918962723</v>
+        <v>0.4975767366720517</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8655737704918033</v>
+        <v>0.5638977635782748</v>
       </c>
       <c r="T28" t="n">
-        <v>0.03662420382165605</v>
+        <v>0.2649310872894334</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3280254777070064</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0625</v>
+        <v>0.2751572327044025</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9792993630573248</v>
+        <v>0.2304075235109718</v>
       </c>
       <c r="X28" t="n">
-        <v>0.974025974025974</v>
+        <v>0.5866454689984102</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.9774557165861514</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.9775641025641025</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9966887417218543</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.6399345335515548</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.9796557120500783</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.9856459330143541</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5252365930599369</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.9688013136288999</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.9803600654664485</v>
+        <v>0.2820097244732577</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.9770867430441899</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.9854604200323102</v>
+        <v>0.5910493827160493</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.9750778816199377</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.9783950617283951</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.9791666666666666</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.9764890282131662</v>
+        <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.9794303797468354</v>
+        <v>0.2085987261146497</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.9751552795031055</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.982484076433121</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.9736408566721582</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.9745627980922098</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0.9788961038961039</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0.957345971563981</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0.9718543046357616</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.9773462783171522</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0.03949447077409163</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.499194847020934</v>
+        <v>0.209375</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.3131955484896661</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6422893481717011</v>
+        <v>0.2635782747603834</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6791530944625407</v>
+        <v>0.1693290734824281</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2818471337579618</v>
+        <v>0.1109271523178808</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3937397034596375</v>
+        <v>0.1950819672131147</v>
       </c>
       <c r="H29" t="n">
-        <v>0.309748427672956</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2939297124600639</v>
+        <v>0.5628930817610063</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3128038897893031</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4248366013071895</v>
+        <v>0.3014586709886548</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3824959481361426</v>
+        <v>0.2496</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02258064516129032</v>
+        <v>0.2884310618066561</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3793677204658902</v>
+        <v>0.8370967741935483</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6427432216905901</v>
+        <v>0.2678288431061807</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3130148270181219</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4278846153846154</v>
+        <v>0.5584</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5048231511254019</v>
+        <v>0.5024390243902439</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5375626043405676</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3135048231511254</v>
+        <v>0.2695252679938744</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5598705501618123</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>0.426984126984127</v>
+        <v>0.273015873015873</v>
       </c>
       <c r="W29" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.2354788069073783</v>
       </c>
       <c r="X29" t="n">
-        <v>0.6168831168831169</v>
+        <v>0.5936</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6086956521739131</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.6119162640901772</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.6184873949579832</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.6399345335515548</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.60625</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.6205787781350482</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6242038216560509</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.6551181102362205</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.6256077795786061</v>
+        <v>0.5893719806763285</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.6026272577996716</v>
+        <v>0.2801302931596091</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.6156405990016639</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.6205787781350482</v>
+        <v>0.5901116427432217</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.6101426307448494</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.6434108527131783</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.6354838709677419</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.6321656050955414</v>
+        <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.197092084006462</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.6018662519440124</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.6420722135007849</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.5970149253731343</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.6151368760064412</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0.6115702479338843</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.6230031948881789</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.8379705400981997</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.6112026359143328</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0.3269537480063796</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1656346749226006</v>
+        <v>0.2279293739967897</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9906542056074766</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9613601236476044</v>
+        <v>0.2549342105263158</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8799368088467614</v>
+        <v>0.1750405186385738</v>
       </c>
       <c r="F30" t="n">
-        <v>0.003081664098613251</v>
+        <v>0.1144781144781145</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006359300476947536</v>
+        <v>0.2039800995024875</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01676829268292683</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.550561797752809</v>
       </c>
       <c r="J30" t="n">
-        <v>0.03475513428120063</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.04088050314465409</v>
+        <v>0.3014827018121911</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0184331797235023</v>
+        <v>0.2580128205128205</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0550314465408805</v>
+        <v>0.2873376623376623</v>
       </c>
       <c r="N30" t="n">
-        <v>0.631496062992126</v>
+        <v>0.8528428093645485</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.2638436482084691</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004784688995215311</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2073732718894009</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1473354231974922</v>
+        <v>0.4983333333333334</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8835725677830941</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="T30" t="n">
-        <v>0.02472952086553323</v>
+        <v>0.2683307332293292</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3020030816640986</v>
+        <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>0.03828483920367534</v>
+        <v>0.2795527156549521</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0.2290322580645161</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0.5862619808306709</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.9969040247678018</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
         <v>1</v>
@@ -5166,34 +4454,34 @@
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.9796557120500783</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.60625</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.9984709480122325</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.9678899082568807</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.4793893129770992</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.9874411302982732</v>
+        <v>0.5848142164781907</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AL30" t="n">
         <v>1</v>
@@ -5208,934 +4496,790 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1</v>
+        <v>0.1976935749588138</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0.9782270606531882</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0.9426751592356688</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0.02752293577981652</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1664074650077761</v>
+        <v>0.231139646869984</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9875195007800313</v>
+        <v>0.304</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9639498432601881</v>
+        <v>0.2601626016260163</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8801261829652997</v>
+        <v>0.1837060702875399</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0046801872074883</v>
+        <v>0.125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.1934959349593496</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01684532924961715</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.003067484662576687</v>
+        <v>0.5489566613162119</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03715170278637771</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.03349282296650718</v>
+        <v>0.2912</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01410658307210031</v>
+        <v>0.2576</v>
       </c>
       <c r="M31" t="n">
-        <v>0.05079365079365079</v>
+        <v>0.2802547770700637</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6419558359621451</v>
+        <v>0.8459016393442623</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9620853080568721</v>
+        <v>0.2614896988906498</v>
       </c>
       <c r="P31" t="n">
-        <v>0.006349206349206349</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.196594427244582</v>
+        <v>0.5431309904153354</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1640378548895899</v>
+        <v>0.4942339373970346</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8788368336025848</v>
+        <v>0.5711974110032363</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0282574568288854</v>
+        <v>0.2635658914728682</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3001555209953344</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>0.03828483920367534</v>
+        <v>0.2733017377567141</v>
       </c>
       <c r="W31" t="n">
-        <v>0.996875</v>
+        <v>0.2318611987381703</v>
       </c>
       <c r="X31" t="n">
-        <v>0.9968652037617555</v>
+        <v>0.5955056179775281</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.9952904238618524</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.9953632148377125</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.9967845659163987</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.9856459330143541</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6205787781350482</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.9984709480122325</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.9672897196261683</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.4838212634822804</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.9843505477308294</v>
+        <v>0.5822784810126582</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.9984101748807631</v>
+        <v>0.2770491803278688</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.9951456310679612</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.9984276729559748</v>
+        <v>0.5808477237048666</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.9969278033794163</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="n">
         <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.9968798751950078</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.9954058192955589</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.9952755905511811</v>
+        <v>0.2087378640776699</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.9954887218045113</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.9953560371517027</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.9952380952380953</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.9952830188679245</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0.9968404423380727</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0.9798761609907121</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0.9968454258675079</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0.02959501557632399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2229102167182662</v>
+        <v>0.239344262295082</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9589905362776026</v>
+        <v>0.3250825082508251</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9251170046801872</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8593508500772797</v>
+        <v>0.2006578947368421</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01533742331288344</v>
+        <v>0.1258389261744967</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04094488188976378</v>
+        <v>0.2115702479338843</v>
       </c>
       <c r="H32" t="n">
-        <v>0.03177004538577912</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01557632398753894</v>
+        <v>0.5339805825242718</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05015673981191222</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.07234726688102894</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0444104134762634</v>
+        <v>0.2734761120263591</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0390625</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6040688575899843</v>
+        <v>0.8360927152317881</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9192546583850931</v>
+        <v>0.2796747967479675</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0141287284144427</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1829457364341085</v>
+        <v>0.5326797385620915</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2074303405572755</v>
+        <v>0.4792013311148087</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8608</v>
+        <v>0.543801652892562</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0375</v>
+        <v>0.2744479495268139</v>
       </c>
       <c r="U32" t="n">
-        <v>0.3569230769230769</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0.07022900763358779</v>
+        <v>0.2908496732026144</v>
       </c>
       <c r="W32" t="n">
-        <v>0.9671361502347418</v>
+        <v>0.2553542009884679</v>
       </c>
       <c r="X32" t="n">
-        <v>0.9541139240506329</v>
+        <v>0.5725938009787929</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.9572107765451664</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.960691823899371</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.9967532467532467</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
         <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.6242038216560509</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.9678899082568807</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.9672897196261683</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.5435114503816794</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.9542586750788643</v>
+        <v>0.5697865353037767</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.9605055292259084</v>
+        <v>0.2944078947368421</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.9600638977635783</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.9654631083202512</v>
+        <v>0.5744336569579288</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.956989247311828</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.9642324888226528</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.9611801242236024</v>
+        <v>1</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.9598765432098766</v>
+        <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.9605678233438486</v>
+        <v>0.2209106239460371</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.9573820395738204</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0.9629629629629629</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.953968253968254</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.9557661927330173</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0.9603803486529319</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.9624413145539906</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0.0426179604261796</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8212121212121212</v>
+        <v>0.2071778140293638</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4923312883435583</v>
+        <v>0.2970779220779221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4878787878787879</v>
+        <v>0.2562814070351759</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5303265940902022</v>
+        <v>0.1694630872483222</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3185298621745788</v>
+        <v>0.1182432432432432</v>
       </c>
       <c r="G33" t="n">
-        <v>0.460093896713615</v>
+        <v>0.1843003412969283</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3388305847076462</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3065250379362671</v>
+        <v>0.5551894563426688</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3323076923076923</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5574803149606299</v>
+        <v>0.2833607907742998</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4854517611026034</v>
+        <v>0.2483552631578947</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>0.284329563812601</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3085443037974683</v>
+        <v>0.8647746243739566</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4773413897280967</v>
+        <v>0.2537067545304778</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3770992366412214</v>
+        <v>0.5635451505016722</v>
       </c>
       <c r="R33" t="n">
-        <v>0.6992248062015504</v>
+        <v>0.5126050420168067</v>
       </c>
       <c r="S33" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.5621890547263682</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3574730354391371</v>
+        <v>0.2551505546751189</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9241486068111455</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5299401197604791</v>
+        <v>0.2612179487179487</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4784615384615384</v>
+        <v>0.2255389718076285</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4720496894409938</v>
+        <v>0.5837479270315091</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4495412844036697</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.4530046224961479</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4588607594936709</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5252365930599369</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.6551181102362205</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.4793893129770992</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.4838212634822804</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.5435114503816794</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.4767801857585139</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.4800613496932515</v>
+        <v>0.2715008431703204</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.4827044025157233</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.4877675840978593</v>
+        <v>0.5980392156862745</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.4769230769230769</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.4681481481481481</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.4884437596302003</v>
+        <v>1</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.4713855421686747</v>
+        <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.1952861952861953</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.4663677130044843</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0.4962292609351433</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.4661417322834646</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.4659442724458204</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0.4818325434439178</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0.4683734939759036</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0.555379746835443</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.4837209302325581</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0.4615384615384616</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1648522550544324</v>
+        <v>0.008090614886731391</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9984177215189873</v>
+        <v>0.117741935483871</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9674418604651163</v>
+        <v>0.1060358890701468</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8944881889763779</v>
+        <v>0.001631321370309951</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0141287284144427</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008090614886731391</v>
+        <v>0.08427876823338736</v>
       </c>
       <c r="H34" t="n">
-        <v>0.02887537993920973</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="I34" t="n">
-        <v>0.007874015748031496</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04423380726698262</v>
+        <v>0.6332794830371568</v>
       </c>
       <c r="K34" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.1062091503267974</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02047244094488189</v>
+        <v>0.06006493506493506</v>
       </c>
       <c r="M34" t="n">
-        <v>0.04983922829581994</v>
+        <v>0.106687898089172</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6463022508038585</v>
+        <v>0.8218954248366013</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9671361502347418</v>
+        <v>0.113452188006483</v>
       </c>
       <c r="P34" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.6089743589743589</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1874015748031496</v>
+        <v>0.9556259904912837</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1414790996784566</v>
+        <v>0.7926421404682275</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8896103896103896</v>
+        <v>0.71875</v>
       </c>
       <c r="T34" t="n">
-        <v>0.03662420382165605</v>
+        <v>0.1095461658841941</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2892690513219285</v>
+        <v>0.5751533742331288</v>
       </c>
       <c r="V34" t="n">
-        <v>0.03255813953488372</v>
+        <v>0.09807073954983923</v>
       </c>
       <c r="W34" t="n">
-        <v>0.9888535031847133</v>
+        <v>0.07532051282051282</v>
       </c>
       <c r="X34" t="n">
-        <v>0.9887459807073955</v>
+        <v>0.6618357487922706</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.9984301412872841</v>
+        <v>0.5836012861736335</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.987460815047022</v>
+        <v>0.587248322147651</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.9901477832512315</v>
+        <v>0.5785953177257525</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.9688013136288999</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.6256077795786061</v>
+        <v>0.5893719806763285</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.9874411302982732</v>
+        <v>0.5848142164781907</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.9843505477308294</v>
+        <v>0.5822784810126582</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.9542586750788643</v>
+        <v>0.5697865353037767</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4767801857585139</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.9905660377358491</v>
+        <v>0.08866995073891626</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.988562091503268</v>
+        <v>0.5896607431340872</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.9889589905362776</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.9890453834115805</v>
+        <v>0.5771704180064309</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.9893939393939394</v>
+        <v>0.5670436187399031</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.987673343605547</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.9907692307692307</v>
+        <v>0.5850556438791733</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.9903225806451613</v>
+        <v>0.01326699834162521</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.9892307692307692</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.9875968992248062</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.9870967741935484</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.9888888888888889</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0.9935275080906149</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0.9813084112149533</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0.9346092503987241</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0.9871175523349437</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0.02664576802507837</v>
+        <v>0.5825242718446602</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1690140845070423</v>
+        <v>0.7675941080196399</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9904912836767037</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9684542586750788</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8781645569620253</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.004716981132075472</v>
+        <v>0.803082191780822</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004885993485342019</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01684532924961715</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.1160130718954248</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0336</v>
+        <v>0.2363636363636364</v>
       </c>
       <c r="K35" t="n">
-        <v>0.03902439024390244</v>
+        <v>0.9932885906040269</v>
       </c>
       <c r="L35" t="n">
-        <v>0.01569858712715855</v>
+        <v>0.9983660130718954</v>
       </c>
       <c r="M35" t="n">
-        <v>0.04133545310015898</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6220095693779905</v>
+        <v>0.17</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9637223974763407</v>
+        <v>0.9966722129783694</v>
       </c>
       <c r="P35" t="n">
-        <v>0.003189792663476874</v>
+        <v>0.2719734660033167</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1871069182389937</v>
+        <v>0.1405228758169935</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1572123176661264</v>
+        <v>0.3310924369747899</v>
       </c>
       <c r="S35" t="n">
-        <v>0.8782467532467533</v>
+        <v>0.3668341708542713</v>
       </c>
       <c r="T35" t="n">
-        <v>0.02834645669291339</v>
+        <v>0.9952</v>
       </c>
       <c r="U35" t="n">
-        <v>0.3034591194968553</v>
+        <v>0.2590266875981161</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0352760736196319</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0.9983579638752053</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.3951219512195122</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.9968798751950078</v>
+        <v>0.2719869706840391</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0.2568965517241379</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.9983606557377049</v>
+        <v>0.2766323024054983</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.9803600654664485</v>
+        <v>0.2820097244732577</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.6026272577996716</v>
+        <v>0.2801302931596091</v>
       </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.9984101748807631</v>
+        <v>0.2770491803278688</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.9605055292259084</v>
+        <v>0.2944078947368421</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.4800613496932515</v>
+        <v>0.2715008431703204</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.9905660377358491</v>
+        <v>0.08866995073891626</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0.2778702163061564</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>0.1206611570247934</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>0.2828618968386024</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>0.2698675496688742</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="AO35" t="n">
-        <v>1</v>
+        <v>0.2671118530884808</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>0.9089376053962901</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0.9843260188087775</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0.9378068739770867</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0.0203125</v>
+        <v>0.2607260726072607</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1708860759493671</v>
+        <v>0.2098569157392687</v>
       </c>
       <c r="C36" t="n">
-        <v>0.992</v>
+        <v>0.2990353697749196</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9682539682539683</v>
+        <v>0.2557755775577558</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8745980707395499</v>
+        <v>0.1630615640599002</v>
       </c>
       <c r="F36" t="n">
-        <v>0.003179650238473768</v>
+        <v>0.1138613861386139</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004901960784313725</v>
+        <v>0.1983606557377049</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0183206106870229</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.5570032573289903</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0275974025974026</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03150912106135987</v>
+        <v>0.2920065252854813</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01271860095389507</v>
+        <v>0.2430213464696223</v>
       </c>
       <c r="M36" t="n">
-        <v>0.05348460291734198</v>
+        <v>0.2875605815831987</v>
       </c>
       <c r="N36" t="n">
-        <v>0.60828025477707</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.2624798711755233</v>
       </c>
       <c r="P36" t="n">
-        <v>0.003311258278145695</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2103559870550162</v>
+        <v>0.5528846153846154</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1598023064250412</v>
+        <v>0.4933110367892977</v>
       </c>
       <c r="S36" t="n">
-        <v>0.8770226537216829</v>
+        <v>0.5475409836065573</v>
       </c>
       <c r="T36" t="n">
-        <v>0.02568218298555377</v>
+        <v>0.2610062893081761</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3039370078740157</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.2673107890499195</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0.232</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0.5849673202614379</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.9967637540453075</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.9983579638752053</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.9770867430441899</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.6156405990016639</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
         <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.9951456310679612</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.9600638977635783</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.4827044025157233</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.988562091503268</v>
+        <v>0.5896607431340872</v>
       </c>
       <c r="AI36" t="n">
-        <v>1</v>
+        <v>0.2778702163061564</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0.5870967741935483</v>
       </c>
       <c r="AL36" t="n">
         <v>1</v>
@@ -6150,306 +5294,258 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1</v>
+        <v>0.2006578947368421</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0.9823151125401929</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0.9408866995073891</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0.0272</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1700468018720749</v>
+        <v>0.006482982171799027</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9906103286384976</v>
+        <v>0.1550888529886914</v>
       </c>
       <c r="D37" t="n">
-        <v>0.966412213740458</v>
+        <v>0.1382636655948553</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8828967642526965</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.003091190108191654</v>
+        <v>0.003252032520325203</v>
       </c>
       <c r="G37" t="n">
-        <v>0.004777070063694267</v>
+        <v>0.1127694859038143</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01804511278195489</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.9967741935483871</v>
       </c>
       <c r="J37" t="n">
-        <v>0.032</v>
+        <v>0.6360655737704918</v>
       </c>
       <c r="K37" t="n">
-        <v>0.03536977491961415</v>
+        <v>0.1506410256410256</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01555209953343701</v>
+        <v>0.1061093247588424</v>
       </c>
       <c r="M37" t="n">
-        <v>0.04610492845786963</v>
+        <v>0.1480891719745223</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6349453978159126</v>
+        <v>0.7933884297520661</v>
       </c>
       <c r="O37" t="n">
-        <v>0.963302752293578</v>
+        <v>0.1601307189542484</v>
       </c>
       <c r="P37" t="n">
-        <v>0.00315955766192733</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1947040498442368</v>
+        <v>0.967479674796748</v>
       </c>
       <c r="R37" t="n">
-        <v>0.1560509554140127</v>
+        <v>0.8286189683860233</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8812199036918138</v>
+        <v>0.7637540453074434</v>
       </c>
       <c r="T37" t="n">
-        <v>0.01901743264659271</v>
+        <v>0.1507936507936508</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3129890453834116</v>
+        <v>0.573394495412844</v>
       </c>
       <c r="V37" t="n">
-        <v>0.03442879499217527</v>
+        <v>0.1374407582938389</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.1136</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.7016129032258065</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.9968553459119497</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>0.5827702702702703</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.9984101748807631</v>
+        <v>0.59</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.9854604200323102</v>
+        <v>0.5910493827160493</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.6205787781350482</v>
+        <v>0.5901116427432217</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.9984276729559748</v>
+        <v>0.5808477237048666</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.9654631083202512</v>
+        <v>0.5744336569579288</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.4877675840978593</v>
+        <v>0.5980392156862745</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.9889589905362776</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0.1206611570247934</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0.5870967741935483</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>0.5748792270531401</v>
       </c>
       <c r="AM37" t="n">
-        <v>1</v>
+        <v>0.5656401944894651</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0.5877483443708609</v>
       </c>
       <c r="AO37" t="n">
-        <v>1</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="AP37" t="n">
-        <v>1</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0.9813664596273292</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0.9429967426710097</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0.02336448598130841</v>
+        <v>0.5841423948220065</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1623277182235835</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9907120743034056</v>
+        <v>0.3121019108280255</v>
       </c>
       <c r="D38" t="n">
-        <v>0.959375</v>
+        <v>0.2622950819672131</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8828967642526965</v>
+        <v>0.1845140032948929</v>
       </c>
       <c r="F38" t="n">
-        <v>0.003076923076923077</v>
+        <v>0.119327731092437</v>
       </c>
       <c r="G38" t="n">
-        <v>0.003110419906687403</v>
+        <v>0.1941272430668842</v>
       </c>
       <c r="H38" t="n">
-        <v>0.02242152466367713</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.5392156862745098</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0359375</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.03164556962025317</v>
+        <v>0.3037156704361874</v>
       </c>
       <c r="L38" t="n">
-        <v>0.009202453987730062</v>
+        <v>0.2681744749596123</v>
       </c>
       <c r="M38" t="n">
-        <v>0.04866562009419152</v>
+        <v>0.2937399678972712</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6697674418604651</v>
+        <v>0.8441127694859039</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9548286604361371</v>
+        <v>0.2669902912621359</v>
       </c>
       <c r="P38" t="n">
-        <v>0.004672897196261682</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1826625386996904</v>
+        <v>0.5463414634146342</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1563467492260062</v>
+        <v>0.480865224625624</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8804523424878837</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="T38" t="n">
-        <v>0.02821316614420063</v>
+        <v>0.2605304212168487</v>
       </c>
       <c r="U38" t="n">
-        <v>0.2896764252696456</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>0.03167420814479638</v>
+        <v>0.2731629392971246</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0.2371794871794872</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0.568659127625202</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.9969135802469136</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.9750778816199377</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.6101426307448494</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.9969278033794163</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.956989247311828</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.4769230769230769</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.9890453834115805</v>
+        <v>0.5771704180064309</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
+        <v>0.2828618968386024</v>
       </c>
       <c r="AJ38" t="n">
         <v>1</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>0.5748792270531401</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
@@ -6464,125 +5560,101 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1</v>
+        <v>0.2061688311688312</v>
       </c>
       <c r="AQ38" t="n">
         <v>1</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.9769585253456221</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0.9381933438985737</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.02147239263803681</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1748878923766816</v>
+        <v>0.2249190938511327</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9908675799086758</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9623493975903614</v>
+        <v>0.2508305647840531</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8781954887218045</v>
+        <v>0.1888701517706577</v>
       </c>
       <c r="F39" t="n">
-        <v>0.003003003003003003</v>
+        <v>0.117056856187291</v>
       </c>
       <c r="G39" t="n">
-        <v>0.006153846153846154</v>
+        <v>0.1873963515754561</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0161764705882353</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.5372168284789643</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03474320241691843</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.03852080123266564</v>
+        <v>0.2773246329526917</v>
       </c>
       <c r="L39" t="n">
-        <v>0.01506024096385542</v>
+        <v>0.2451298701298701</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05513016845329249</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6621004566210046</v>
+        <v>0.8511705685618729</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9578947368421052</v>
+        <v>0.2552845528455285</v>
       </c>
       <c r="P39" t="n">
-        <v>0.004622496147919877</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2018209408194234</v>
+        <v>0.5387096774193548</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1598173515981735</v>
+        <v>0.4822335025380711</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8767550702028081</v>
+        <v>0.5473856209150327</v>
       </c>
       <c r="T39" t="n">
-        <v>0.02413273001508296</v>
+        <v>0.254746835443038</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3070044709388972</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>0.03582089552238806</v>
+        <v>0.2619808306709265</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0.2302631578947368</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0.567479674796748</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.996996996996997</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.998468606431853</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9783950617283951</v>
+        <v>1</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.6434108527131783</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="n">
         <v>1</v>
@@ -6591,22 +5663,22 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.9642324888226528</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.4681481481481481</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.9893939393939394</v>
+        <v>0.5670436187399031</v>
       </c>
       <c r="AI39" t="n">
-        <v>1</v>
+        <v>0.2698675496688742</v>
       </c>
       <c r="AJ39" t="n">
         <v>1</v>
       </c>
       <c r="AK39" t="n">
-        <v>1</v>
+        <v>0.5656401944894651</v>
       </c>
       <c r="AL39" t="n">
         <v>1</v>
@@ -6621,113 +5693,89 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>0.1976935749588138</v>
       </c>
       <c r="AQ39" t="n">
         <v>1</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.978978978978979</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0.9480122324159022</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.02529761904761905</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.174922600619195</v>
+        <v>0.2070707070707071</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9905362776025236</v>
+        <v>0.2793388429752066</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9625</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="E40" t="n">
-        <v>0.881619937694704</v>
+        <v>0.1621160409556314</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0046801872074883</v>
+        <v>0.09930313588850175</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004792332268370607</v>
+        <v>0.1689419795221843</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02265861027190332</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03448275862068965</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.2628865979381443</v>
       </c>
       <c r="L40" t="n">
-        <v>0.01547987616099071</v>
+        <v>0.2243150684931507</v>
       </c>
       <c r="M40" t="n">
-        <v>0.04416403785488959</v>
+        <v>0.2595041322314049</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6311605723370429</v>
+        <v>0.8687392055267703</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9582689335394127</v>
+        <v>0.2354892205638474</v>
       </c>
       <c r="P40" t="n">
-        <v>0.00473186119873817</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1918876755070203</v>
+        <v>0.5440931780366056</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1576433121019108</v>
+        <v>0.4715025906735751</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8806451612903226</v>
+        <v>0.537542662116041</v>
       </c>
       <c r="T40" t="n">
-        <v>0.03322784810126582</v>
+        <v>0.2320261437908497</v>
       </c>
       <c r="U40" t="n">
-        <v>0.3059006211180124</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0.03215926493108729</v>
+        <v>0.2471358428805237</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0.2157190635451505</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0.5641891891891891</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.9968847352024922</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
@@ -6736,34 +5784,34 @@
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.9791666666666666</v>
+        <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.6354838709677419</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.9968798751950078</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.9611801242236024</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.4884437596302003</v>
+        <v>1</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.987673343605547</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="AI40" t="n">
-        <v>1</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="AJ40" t="n">
         <v>1</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0.5877483443708609</v>
       </c>
       <c r="AL40" t="n">
         <v>1</v>
@@ -6778,149 +5826,125 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1</v>
+        <v>0.1701030927835052</v>
       </c>
       <c r="AQ40" t="n">
         <v>1</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0.9782270606531882</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0.9496062992125984</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.0265210608424337</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1706948640483384</v>
+        <v>0.2191558441558442</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9908116385911179</v>
+        <v>0.2957516339869281</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9738058551617874</v>
+        <v>0.254180602006689</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8950617283950617</v>
+        <v>0.1810766721044046</v>
       </c>
       <c r="F41" t="n">
-        <v>0.003058103975535168</v>
+        <v>0.1116666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00625</v>
+        <v>0.18561872909699</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01777777777777778</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.5464926590538336</v>
       </c>
       <c r="J41" t="n">
-        <v>0.03421461897356143</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.03416149068322982</v>
+        <v>0.2911184210526316</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01671732522796352</v>
+        <v>0.2536585365853659</v>
       </c>
       <c r="M41" t="n">
-        <v>0.05084745762711865</v>
+        <v>0.2781350482315113</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6217054263565891</v>
+        <v>0.8431703204047217</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.247557003257329</v>
       </c>
       <c r="P41" t="n">
-        <v>0.004629629629629629</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1972477064220184</v>
+        <v>0.5548281505728314</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1599378881987578</v>
+        <v>0.4875207986688852</v>
       </c>
       <c r="S41" t="n">
-        <v>0.8954041204437401</v>
+        <v>0.5508196721311476</v>
       </c>
       <c r="T41" t="n">
-        <v>0.02476780185758514</v>
+        <v>0.2567353407290016</v>
       </c>
       <c r="U41" t="n">
-        <v>0.2974203338391502</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>0.03338391502276176</v>
+        <v>0.2625607779578606</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.226904376012966</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0.5781758957654723</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.9969325153374233</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.9984025559105432</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.9764890282131662</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.6321656050955414</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>1</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.9954058192955589</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.9598765432098766</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.4713855421686747</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.9907692307692307</v>
+        <v>0.5850556438791733</v>
       </c>
       <c r="AI41" t="n">
-        <v>1</v>
+        <v>0.2671118530884808</v>
       </c>
       <c r="AJ41" t="n">
         <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>1</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="AL41" t="n">
         <v>1</v>
@@ -6935,306 +5959,258 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1</v>
+        <v>0.1959798994974874</v>
       </c>
       <c r="AQ41" t="n">
         <v>1</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0.9891975308641975</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0.9441860465116279</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.0248062015503876</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1622464898595944</v>
+        <v>0.9379084967320261</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9921383647798742</v>
+        <v>0.8564356435643564</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9636650868878357</v>
+        <v>0.8777219430485762</v>
       </c>
       <c r="E42" t="n">
-        <v>0.886762360446571</v>
+        <v>0.9261744966442953</v>
       </c>
       <c r="F42" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.928082191780822</v>
       </c>
       <c r="G42" t="n">
-        <v>0.003125</v>
+        <v>0.8892561983471075</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0182370820668693</v>
+        <v>0.006633499170812604</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.01990049751243781</v>
       </c>
       <c r="J42" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.1503378378378378</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0368</v>
+        <v>0.8631051752921536</v>
       </c>
       <c r="L42" t="n">
-        <v>0.01564945226917058</v>
+        <v>0.9055374592833876</v>
       </c>
       <c r="M42" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.8629690048939641</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6141732283464567</v>
+        <v>0.09661016949152543</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9595015576323987</v>
+        <v>0.8606965174129353</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0032</v>
+        <v>0.2042833607907743</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.196875</v>
+        <v>0.04597701149425287</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1518578352180937</v>
+        <v>0.1942078364565588</v>
       </c>
       <c r="S42" t="n">
-        <v>0.887459807073955</v>
+        <v>0.2345058626465662</v>
       </c>
       <c r="T42" t="n">
-        <v>0.02830188679245283</v>
+        <v>0.8675282714054927</v>
       </c>
       <c r="U42" t="n">
-        <v>0.293103448275862</v>
+        <v>0.1874015748031496</v>
       </c>
       <c r="V42" t="n">
-        <v>0.02945736434108527</v>
+        <v>0.8962108731466227</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0.9208400646203554</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0.2627257799671593</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.9984177215189873</v>
+        <v>0.2094155844155844</v>
       </c>
       <c r="Z42" t="n">
-        <v>1</v>
+        <v>0.2050847457627119</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.9984</v>
+        <v>0.1907216494845361</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.9794303797468354</v>
+        <v>0.2085987261146497</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.197092084006462</v>
       </c>
       <c r="AD42" t="n">
-        <v>1</v>
+        <v>0.1976935749588138</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.9952755905511811</v>
+        <v>0.2087378640776699</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.9605678233438486</v>
+        <v>0.2209106239460371</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.1952861952861953</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.9903225806451613</v>
+        <v>0.01326699834162521</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>0.9089376053962901</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>0.2006578947368421</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="AL42" t="n">
-        <v>1</v>
+        <v>0.2061688311688312</v>
       </c>
       <c r="AM42" t="n">
-        <v>1</v>
+        <v>0.1976935749588138</v>
       </c>
       <c r="AN42" t="n">
-        <v>1</v>
+        <v>0.1701030927835052</v>
       </c>
       <c r="AO42" t="n">
-        <v>1</v>
+        <v>0.1959798994974874</v>
       </c>
       <c r="AP42" t="n">
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0.9782608695652174</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0.9448946515397083</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0.02627511591962906</v>
+        <v>0.1865793780687398</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1591591591591592</v>
+        <v>0.2106109324758842</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9906396255850234</v>
+        <v>0.2878048780487805</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9727272727272728</v>
+        <v>0.2455284552845528</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8715596330275229</v>
+        <v>0.1783333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001506024096385542</v>
+        <v>0.1122278056951424</v>
       </c>
       <c r="G43" t="n">
-        <v>0.006182380216383307</v>
+        <v>0.180921052631579</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01756954612005857</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.5400981996726678</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0289193302891933</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.03426791277258567</v>
+        <v>0.2887096774193548</v>
       </c>
       <c r="L43" t="n">
-        <v>0.01374045801526718</v>
+        <v>0.2312703583061889</v>
       </c>
       <c r="M43" t="n">
-        <v>0.04747320061255743</v>
+        <v>0.2669826224328594</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6321483771251932</v>
+        <v>0.8590381426202321</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9700149925037481</v>
+        <v>0.2507987220447284</v>
       </c>
       <c r="P43" t="n">
-        <v>0.00310077519379845</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2006079027355623</v>
+        <v>0.5571658615136876</v>
       </c>
       <c r="R43" t="n">
-        <v>0.1496913580246914</v>
+        <v>0.4917218543046358</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8711180124223602</v>
+        <v>0.5598006644518272</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0258751902587519</v>
+        <v>0.242472266244057</v>
       </c>
       <c r="U43" t="n">
-        <v>0.2861491628614916</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0.03288490284005979</v>
+        <v>0.2536824877250409</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0.2080645161290323</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0.5890850722311396</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.9968992248062015</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.9984399375975039</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.9751552795031055</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.6018662519440124</v>
+        <v>1</v>
       </c>
       <c r="AD43" t="n">
         <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.9954887218045113</v>
+        <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.9573820395738204</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.4663677130044843</v>
+        <v>1</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.9892307692307692</v>
+        <v>0.5825242718446602</v>
       </c>
       <c r="AI43" t="n">
-        <v>1</v>
+        <v>0.2607260726072607</v>
       </c>
       <c r="AJ43" t="n">
         <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>1</v>
+        <v>0.5841423948220065</v>
       </c>
       <c r="AL43" t="n">
         <v>1</v>
@@ -7249,1289 +6225,9 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1</v>
+        <v>0.1865793780687398</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0.9863013698630136</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0.9383886255924171</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.01984732824427481</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.1794478527607362</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.9891304347826086</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.963302752293578</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.8809160305343512</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.004573170731707317</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.00631911532385466</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.01497005988023952</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.03072196620583717</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.03827751196172249</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.0182370820668693</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.04636785162287481</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.6191950464396285</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.9585253456221198</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.004658385093167702</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.1931993817619784</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.162754303599374</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.8760064412238325</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0.02469135802469136</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.3134556574923548</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.03469079939668175</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.9969230769230769</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.9984076433121019</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.982484076433121</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.6420722135007849</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.9953560371517027</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.9629629629629629</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.4962292609351433</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.9875968992248062</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0.9800613496932515</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0.9525316455696202</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.02635658914728682</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.15600624024961</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.9886914378029079</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.9618441971383148</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.882258064516129</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.004709576138147566</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.001594896331738437</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.0171875</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.0322061191626409</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.02295081967213115</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.01102362204724409</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.06022187004754358</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.7186495176848875</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.9587955625990491</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.004830917874396135</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.1844197138314785</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.1375404530744337</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.8856682769726248</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.02243589743589744</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.2750397456279809</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.02034428794992175</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0.9968152866242038</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.9983277591973244</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.9736408566721582</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.5970149253731343</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0.9952380952380953</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.953968253968254</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.4661417322834646</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.9870967741935484</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0.9779527559055118</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0.9392446633825944</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0.02396166134185303</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.170015455950541</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.990521327014218</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.8670886075949367</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.004622496147919877</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.006289308176100629</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.02137404580152672</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.03508771929824561</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.03745928338762215</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.0171606864274571</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.05039370078740157</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.606973058637084</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.9594383775351014</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.2044025157232705</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.8661290322580645</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0.0297339593114241</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.2877358490566038</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0.03400309119010819</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0.9968404423380727</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.99836867862969</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.9745627980922098</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.6151368760064412</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.9952830188679245</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.9557661927330173</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.4659442724458204</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.9888888888888889</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0.9766355140186916</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0.9429037520391517</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0.02777777777777778</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.1773940345368917</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.9919614147909968</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.9648562300319489</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.8760064412238325</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.004724409448818898</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.02153846153846154</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.03709677419354838</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.03618421052631579</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.01587301587301587</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.04313099041533546</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.5984</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.9603803486529319</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.004784688995215311</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.1894904458598726</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.1696574225122349</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.8778501628664495</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.02889245585874799</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.307936507936508</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.03149606299212598</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0.9983974358974359</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.9983552631578947</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.9788961038961039</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.6115702479338843</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.9968404423380727</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.9603803486529319</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.4818325434439178</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.9935275080906149</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0.98125</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0.9441707717569786</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0.02715654952076677</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.1689497716894977</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.9921383647798742</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.8826291079812206</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.02153846153846154</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.02556390977443609</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.01545595054095827</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.05696202531645569</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.05414012738853503</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.02439024390243903</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.04821150855365474</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.616822429906542</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.01572327044025157</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.2194744976816074</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.168503937007874</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.8857589984350548</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.04205607476635514</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.0453857791225416</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.9797191887675507</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.9795597484276729</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0.9796557120500783</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.9844961240310077</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.9823434991974318</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.957345971563981</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.6230031948881789</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.9782270606531882</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0.9798761609907121</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.4683734939759036</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.9813084112149533</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.9843260188087775</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.9823151125401929</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0.9813664596273292</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0.9769585253456221</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.978978978978979</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0.9782270606531882</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0.9891975308641975</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.9782608695652174</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.9863013698630136</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0.9800613496932515</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.9779527559055118</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.9766355140186916</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0.98125</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0.9764150943396226</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0.03533026113671275</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.2372611464968153</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.9451612903225807</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9307086614173228</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.8460291734197731</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.03194888178913738</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.04665629860031104</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.03354632587859425</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.05617977528089887</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.09634551495016612</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.04383116883116883</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.5970636215334421</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.9418238993710691</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0.03079416531604538</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0.2304</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.224390243902439</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.8590381426202321</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.06220095693779904</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.3656597774244833</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.08253968253968254</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.9406099518459069</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.9453376205787781</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.9421221864951769</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0.946515397082658</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.9586776859504132</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.9718543046357616</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0.8379705400981997</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.9426751592356688</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.555379746835443</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.9346092503987241</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0.9378068739770867</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.9408866995073891</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0.9429967426710097</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0.9381933438985737</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.9480122324159022</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0.9496062992125984</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0.9441860465116279</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.9448946515397083</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.9383886255924171</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0.9525316455696202</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.9392446633825944</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.9429037520391517</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0.9441707717569786</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.9414634146341463</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0.06507936507936508</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.1677215189873418</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.9585326953748007</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.869701726844584</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.004746835443037975</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.004777070063694267</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.01846153846153846</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.03486529318541997</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.04045307443365696</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.01567398119122257</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.03709677419354838</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.6340288924558587</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.9544025157232704</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0.003225806451612903</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.196875</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.1515151515151515</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.8701923076923077</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.02702702702702703</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.3037974683544304</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0.034375</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0.9968503937007874</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.9773462783171522</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0.6112026359143328</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0.9968454258675079</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.9624413145539906</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.4837209302325581</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0.9871175523349437</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0.9764150943396226</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0.9414634146341463</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0.02037617554858934</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.7420333839150227</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0330188679245283</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.05376344086021505</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.1286821705426357</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.8531684698608965</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.8149920255183413</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.8272727272727273</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.8792569659442725</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.8053375196232339</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.7733755942947702</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.8133748055987559</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.007936507936507936</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.05909797822706065</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0.9589257503949447</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.7864823348694316</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.7338582677165354</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.1233974358974359</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.8287037037037037</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.6594761171032357</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0.7914110429447853</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.0249221183800623</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.02511773940345369</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0.02018633540372671</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.0170015455950541</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.02898550724637681</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.03949447077409163</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.3269537480063796</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.02752293577981652</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0.02959501557632399</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.0426179604261796</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.02664576802507837</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.0203125</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.0272</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0.02336448598130841</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0.02147239263803681</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.02529761904761905</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0.0265210608424337</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0.0248062015503876</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.02627511591962906</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.01984732824427481</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.02635658914728682</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.02396166134185303</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.02777777777777778</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0.02715654952076677</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.03533026113671275</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.06507936507936508</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.02037617554858934</v>
-      </c>
-      <c r="AY51" t="n">
         <v>1</v>
       </c>
     </row>
